--- a/reports/Angola_3.1.3_import_top_25_partners_2003-2024.xlsx
+++ b/reports/Angola_3.1.3_import_top_25_partners_2003-2024.xlsx
@@ -3792,121 +3792,121 @@
         <v>44</v>
       </c>
       <c r="D16">
-        <v>0.003192701619815057</v>
+        <v>0.003192744471469164</v>
       </c>
       <c r="E16">
-        <v>0.006200076594685191</v>
+        <v>0.006200159810584861</v>
       </c>
       <c r="F16">
-        <v>0.03482482840406173</v>
+        <v>0.03482529581432389</v>
       </c>
       <c r="G16">
-        <v>0.002941197782242703</v>
+        <v>0.0029412372582743</v>
       </c>
       <c r="H16">
-        <v>0.2006244849612454</v>
+        <v>0.2006271776936265</v>
       </c>
       <c r="I16">
-        <v>0.005231540681077104</v>
+        <v>0.005231610897526496</v>
       </c>
       <c r="J16">
-        <v>0.04819095697500016</v>
+        <v>0.0481916037821451</v>
       </c>
       <c r="K16">
-        <v>0.03673449877265383</v>
+        <v>0.03673499181404092</v>
       </c>
       <c r="L16">
-        <v>0.03633740273881136</v>
+        <v>0.03633789045047336</v>
       </c>
       <c r="M16">
-        <v>0.005372151829143143</v>
+        <v>0.005372223932840702</v>
       </c>
       <c r="N16">
-        <v>0.02015375610159782</v>
+        <v>0.0201540266003441</v>
       </c>
       <c r="O16">
-        <v>0.01466067081044794</v>
+        <v>0.01466086758235755</v>
       </c>
       <c r="P16">
-        <v>0.007392641813463998</v>
+        <v>0.007392741035680053</v>
       </c>
       <c r="Q16">
-        <v>0.01542579287873927</v>
+        <v>0.01542599991992867</v>
       </c>
       <c r="R16">
-        <v>0.00446312163670393</v>
+        <v>0.00446318153962233</v>
       </c>
       <c r="S16">
-        <v>0.02545157623850001</v>
+        <v>0.0254519178432822</v>
       </c>
       <c r="T16">
-        <v>0.004395434336888888</v>
+        <v>0.004395493331325036</v>
       </c>
       <c r="U16">
-        <v>0.002457683383691189</v>
+        <v>0.00245771637011172</v>
       </c>
       <c r="V16">
-        <v>0.01115924357126764</v>
+        <v>0.01115939334788399</v>
       </c>
       <c r="W16">
-        <v>0.01373540371732612</v>
+        <v>0.01373558807052889</v>
       </c>
       <c r="X16">
-        <v>0.003503613322285432</v>
+        <v>0.003503660346919766</v>
       </c>
       <c r="Y16">
-        <v>0.01557900438023844</v>
+        <v>0.01557921347779484</v>
       </c>
       <c r="Z16">
-        <v>0.0006948105627640019</v>
+        <v>0.0006948198883400972</v>
       </c>
       <c r="AA16">
-        <v>0.001486133151742111</v>
+        <v>0.001486153098254926</v>
       </c>
       <c r="AB16">
-        <v>0.1256494493310057</v>
+        <v>0.1256511357669407</v>
       </c>
       <c r="AC16">
-        <v>0.1003267373681156</v>
+        <v>0.100328083928853</v>
       </c>
       <c r="AD16">
-        <v>0.007523482812310521</v>
+        <v>0.007523583790642209</v>
       </c>
       <c r="AE16">
-        <v>0.02268477639137653</v>
+        <v>0.02268508086085322</v>
       </c>
       <c r="AF16">
-        <v>0.036374490006989</v>
+        <v>0.03637497821642717</v>
       </c>
       <c r="AG16">
-        <v>0.01237499857029802</v>
+        <v>0.01237516466447826</v>
       </c>
       <c r="AH16">
-        <v>0.002387434957650399</v>
+        <v>0.002387467001213872</v>
       </c>
       <c r="AI16">
-        <v>0.001236948867608907</v>
+        <v>0.001236965469631687</v>
       </c>
       <c r="AJ16">
-        <v>0.009841036824382804</v>
+        <v>0.009841168908353142</v>
       </c>
       <c r="AK16">
-        <v>0.0002264257249427335</v>
+        <v>0.0002264287639729973</v>
       </c>
       <c r="AL16">
-        <v>0.01275926116545529</v>
+        <v>0.01275943241711336</v>
       </c>
       <c r="AM16">
-        <v>0.06294092058463942</v>
+        <v>0.0629417653621599</v>
       </c>
       <c r="AN16">
-        <v>0.01475013875026171</v>
+        <v>0.01475033672298795</v>
       </c>
       <c r="AO16">
-        <v>0.03770546025027886</v>
+        <v>0.03770596632367154</v>
       </c>
       <c r="AP16">
-        <v>0.002497771802160757</v>
+        <v>0.002497805326638158</v>
       </c>
       <c r="AQ16">
         <v>59153984.54</v>
@@ -4282,121 +4282,121 @@
         <v>44</v>
       </c>
       <c r="D18">
-        <v>0.003132241318831776</v>
+        <v>0.003132239939614713</v>
       </c>
       <c r="E18">
-        <v>0.008564949460877052</v>
+        <v>0.008564945689480394</v>
       </c>
       <c r="F18">
-        <v>0.05644823447325233</v>
+        <v>0.05644820961745092</v>
       </c>
       <c r="G18">
-        <v>0.005251950900582576</v>
+        <v>0.005251948587995658</v>
       </c>
       <c r="H18">
-        <v>0.190065505996914</v>
+        <v>0.190065422305537</v>
       </c>
       <c r="I18">
-        <v>0.002231407472950556</v>
+        <v>0.002231406490396867</v>
       </c>
       <c r="J18">
-        <v>0.04376543010894759</v>
+        <v>0.04376541083775427</v>
       </c>
       <c r="K18">
-        <v>0.001627296702966446</v>
+        <v>0.001627295986420321</v>
       </c>
       <c r="L18">
-        <v>0.02881682857346611</v>
+        <v>0.02881681588457734</v>
       </c>
       <c r="M18">
-        <v>0.001406002229329114</v>
+        <v>0.00140600161022539</v>
       </c>
       <c r="N18">
-        <v>0.02454883220701494</v>
+        <v>0.02454882139744926</v>
       </c>
       <c r="O18">
-        <v>0.01965426944520691</v>
+        <v>0.01965426079085974</v>
       </c>
       <c r="P18">
-        <v>0.007592108629231047</v>
+        <v>0.007592105286204536</v>
       </c>
       <c r="Q18">
-        <v>0.02673960307477054</v>
+        <v>0.02673959130054465</v>
       </c>
       <c r="R18">
-        <v>0.002600152062653561</v>
+        <v>0.002600150917730891</v>
       </c>
       <c r="S18">
-        <v>0.01873506737058037</v>
+        <v>0.01873505912098465</v>
       </c>
       <c r="T18">
-        <v>0.0002454560591185863</v>
+        <v>0.0002454559510371358</v>
       </c>
       <c r="U18">
-        <v>0.003746880129712455</v>
+        <v>0.003746878479852025</v>
       </c>
       <c r="V18">
-        <v>0.005003554058986473</v>
+        <v>0.005003551855775918</v>
       </c>
       <c r="W18">
-        <v>0.01426549477210885</v>
+        <v>0.01426548849059609</v>
       </c>
       <c r="X18">
-        <v>0.007521543958606542</v>
+        <v>0.007521540646651711</v>
       </c>
       <c r="Y18">
-        <v>0.0139152081195507</v>
+        <v>0.01391520199227936</v>
       </c>
       <c r="Z18">
-        <v>0.002445036714399986</v>
+        <v>0.002445035637779122</v>
       </c>
       <c r="AA18">
-        <v>0.001776104447563334</v>
+        <v>0.001776103665492825</v>
       </c>
       <c r="AB18">
-        <v>0.1697997404275705</v>
+        <v>0.1697996656598002</v>
       </c>
       <c r="AC18">
-        <v>0.02852883732732294</v>
+        <v>0.02852882476524511</v>
       </c>
       <c r="AD18">
-        <v>0.01083417156522901</v>
+        <v>0.01083416679462778</v>
       </c>
       <c r="AE18">
-        <v>0.005546520856765592</v>
+        <v>0.005546518414470945</v>
       </c>
       <c r="AF18">
-        <v>0.04893333899494783</v>
+        <v>0.04893331744817373</v>
       </c>
       <c r="AG18">
-        <v>0.02231263667040533</v>
+        <v>0.02231262684550166</v>
       </c>
       <c r="AH18">
-        <v>0.0006459781933342638</v>
+        <v>0.0006459779088912545</v>
       </c>
       <c r="AI18">
-        <v>0.0007483001449217266</v>
+        <v>0.0007482998154233823</v>
       </c>
       <c r="AJ18">
-        <v>0.01558155794936378</v>
+        <v>0.01558155108835008</v>
       </c>
       <c r="AK18">
-        <v>0.0008492898153696302</v>
+        <v>0.0008492894414025932</v>
       </c>
       <c r="AL18">
-        <v>0.01591917473745617</v>
+        <v>0.01591916772777997</v>
       </c>
       <c r="AM18">
-        <v>0.0681550286420049</v>
+        <v>0.06815499863136112</v>
       </c>
       <c r="AN18">
-        <v>0.03279124335983077</v>
+        <v>0.03279122892089144</v>
       </c>
       <c r="AO18">
-        <v>0.04153706962919577</v>
+        <v>0.04153705133921446</v>
       </c>
       <c r="AP18">
-        <v>0.003166053759443275</v>
+        <v>0.00316605236533761</v>
       </c>
       <c r="AQ18">
         <v>37202375.2</v>
@@ -4527,121 +4527,121 @@
         <v>44</v>
       </c>
       <c r="D19">
-        <v>0.003605619342277326</v>
+        <v>0.003605600002822385</v>
       </c>
       <c r="E19">
-        <v>0.02267168595213162</v>
+        <v>0.02267156434804442</v>
       </c>
       <c r="F19">
-        <v>0.04419718559987078</v>
+        <v>0.04419694853949412</v>
       </c>
       <c r="G19">
-        <v>0.004891777857606873</v>
+        <v>0.004891751619585475</v>
       </c>
       <c r="H19">
-        <v>0.2176866420070802</v>
+        <v>0.217685474401572</v>
       </c>
       <c r="I19">
-        <v>0.003015124425647995</v>
+        <v>0.003015108253429734</v>
       </c>
       <c r="J19">
-        <v>0.0263847970003853</v>
+        <v>0.02638465548029006</v>
       </c>
       <c r="K19">
-        <v>0.001178996337019866</v>
+        <v>0.00117899001323902</v>
       </c>
       <c r="L19">
-        <v>0.03060463020033581</v>
+        <v>0.03060446604632771</v>
       </c>
       <c r="M19">
-        <v>0.001625397335522621</v>
+        <v>0.001625388617381423</v>
       </c>
       <c r="N19">
-        <v>0.01583463007568432</v>
+        <v>0.01583454514350325</v>
       </c>
       <c r="O19">
-        <v>0.02610502377288802</v>
+        <v>0.02610488375341202</v>
       </c>
       <c r="P19">
-        <v>0.008844842150375461</v>
+        <v>0.008844794709309173</v>
       </c>
       <c r="Q19">
-        <v>0.02278325472708285</v>
+        <v>0.02278313252457439</v>
       </c>
       <c r="R19">
-        <v>0.001925408670344039</v>
+        <v>0.001925398343032505</v>
       </c>
       <c r="S19">
-        <v>0.01671064966046512</v>
+        <v>0.01671056002957915</v>
       </c>
       <c r="T19">
-        <v>0.0002331412495147376</v>
+        <v>0.0002331399990153749</v>
       </c>
       <c r="U19">
-        <v>0.003147661074164535</v>
+        <v>0.003147644191059655</v>
       </c>
       <c r="V19">
-        <v>0.00497660261583803</v>
+        <v>0.004976575922842206</v>
       </c>
       <c r="W19">
-        <v>0.01558178897742455</v>
+        <v>0.01558170540140689</v>
       </c>
       <c r="X19">
-        <v>2.854282212533931E-05</v>
+        <v>2.854266903024802E-05</v>
       </c>
       <c r="Y19">
-        <v>0.015638045735298</v>
+        <v>0.01563796185753605</v>
       </c>
       <c r="Z19">
-        <v>0.003139684026999736</v>
+        <v>0.003139667186681331</v>
       </c>
       <c r="AA19">
-        <v>0.001353769974482696</v>
+        <v>0.001353762713268758</v>
       </c>
       <c r="AB19">
-        <v>0.1862649478873402</v>
+        <v>0.1862639488183247</v>
       </c>
       <c r="AC19">
-        <v>0.01543058672192091</v>
+        <v>0.01543050395690655</v>
       </c>
       <c r="AD19">
-        <v>0.004779469963124906</v>
+        <v>0.004779444327489189</v>
       </c>
       <c r="AE19">
-        <v>0.00564809017859036</v>
+        <v>0.005648059883937725</v>
       </c>
       <c r="AF19">
-        <v>0.0469881918490475</v>
+        <v>0.04698793981855489</v>
       </c>
       <c r="AG19">
-        <v>0.01021767032731073</v>
+        <v>0.01021761552280806</v>
       </c>
       <c r="AH19">
-        <v>0.001065565261440201</v>
+        <v>0.001065559546069441</v>
       </c>
       <c r="AI19">
-        <v>0.002144493107325362</v>
+        <v>0.002144481604910969</v>
       </c>
       <c r="AJ19">
-        <v>0.02036275056145247</v>
+        <v>0.02036264134179849</v>
       </c>
       <c r="AK19">
-        <v>0.01890258827153873</v>
+        <v>0.01890248688375498</v>
       </c>
       <c r="AL19">
-        <v>0.02255597276625964</v>
+        <v>0.02255585178282309</v>
       </c>
       <c r="AM19">
-        <v>0.05074076505314317</v>
+        <v>0.05074049289497942</v>
       </c>
       <c r="AN19">
-        <v>0.05181622809449534</v>
+        <v>0.05181595016787212</v>
       </c>
       <c r="AO19">
-        <v>0.02551897893444112</v>
+        <v>0.02551884205833292</v>
       </c>
       <c r="AP19">
-        <v>0.00386336859136645</v>
+        <v>0.003863347869422257</v>
       </c>
       <c r="AQ19">
         <v>37319491.26</v>
@@ -5017,121 +5017,121 @@
         <v>44</v>
       </c>
       <c r="D21">
-        <v>0.005023081012624019</v>
+        <v>0.005032632739363416</v>
       </c>
       <c r="E21">
-        <v>0.01815291378295615</v>
+        <v>0.01818743277071343</v>
       </c>
       <c r="F21">
-        <v>0.04605625092605884</v>
+        <v>0.04614382998806903</v>
       </c>
       <c r="G21">
-        <v>0.01392829390789023</v>
+        <v>0.01395477949651996</v>
       </c>
       <c r="H21">
-        <v>0.2298212293852774</v>
+        <v>0.2302582499263523</v>
       </c>
       <c r="I21">
-        <v>0.003753765306560126</v>
+        <v>0.003760903344023982</v>
       </c>
       <c r="J21">
-        <v>0.008735822572444598</v>
+        <v>0.008752434327231377</v>
       </c>
       <c r="K21">
-        <v>0.0009766051835079274</v>
+        <v>0.0009784622640172207</v>
       </c>
       <c r="L21">
-        <v>0.03236376391459382</v>
+        <v>0.03054575198454494</v>
       </c>
       <c r="M21">
-        <v>0.01890655855203899</v>
+        <v>0.01894251064606607</v>
       </c>
       <c r="N21">
-        <v>0.01851397542401365</v>
+        <v>0.01854918099479096</v>
       </c>
       <c r="O21">
-        <v>0.03170175504115434</v>
+        <v>0.03176203806278018</v>
       </c>
       <c r="P21">
-        <v>0.01317619571571067</v>
+        <v>0.01320125113899072</v>
       </c>
       <c r="Q21">
-        <v>0.02838609246247671</v>
+        <v>0.02844007052847235</v>
       </c>
       <c r="R21">
-        <v>0.004045223105489799</v>
+        <v>0.004052915369581583</v>
       </c>
       <c r="S21">
-        <v>0.01853579755059077</v>
+        <v>0.018571044617611</v>
       </c>
       <c r="T21">
-        <v>0.0005179868356309604</v>
+        <v>0.0005189718224739193</v>
       </c>
       <c r="U21">
-        <v>0.001845051064558462</v>
+        <v>0.001848559553381279</v>
       </c>
       <c r="V21">
-        <v>0.003321131383211142</v>
+        <v>0.003327446738141381</v>
       </c>
       <c r="W21">
-        <v>0.02275900274840049</v>
+        <v>0.02280228052444423</v>
       </c>
       <c r="X21">
-        <v>9.4589298692857E-05</v>
+        <v>9.476916661282776E-05</v>
       </c>
       <c r="Y21">
-        <v>0.01917153795807499</v>
+        <v>0.01920799392828317</v>
       </c>
       <c r="Z21">
-        <v>0.0008850025448446716</v>
+        <v>0.0008866854367691263</v>
       </c>
       <c r="AA21">
-        <v>0.001774332716229838</v>
+        <v>0.001777706729351984</v>
       </c>
       <c r="AB21">
-        <v>0.1306910190988791</v>
+        <v>0.1309395368708578</v>
       </c>
       <c r="AC21">
-        <v>0.01053854423744535</v>
+        <v>0.01055858398885173</v>
       </c>
       <c r="AD21">
-        <v>0.0104416476805569</v>
+        <v>0.01046150317663651</v>
       </c>
       <c r="AE21">
-        <v>0.01550102966227308</v>
+        <v>0.01553050591382889</v>
       </c>
       <c r="AF21">
-        <v>0.04590775167649021</v>
+        <v>0.04599504835717919</v>
       </c>
       <c r="AG21">
-        <v>0.01305504025768588</v>
+        <v>0.01307986529570534</v>
       </c>
       <c r="AH21">
-        <v>0.001638349355770794</v>
+        <v>0.001641464787377543</v>
       </c>
       <c r="AI21">
-        <v>0.002741292537124966</v>
+        <v>0.002746505289449995</v>
       </c>
       <c r="AJ21">
-        <v>0.02363209296028715</v>
+        <v>0.02367703097615219</v>
       </c>
       <c r="AK21">
-        <v>2.737786758042324E-06</v>
+        <v>2.742992843892391E-06</v>
       </c>
       <c r="AL21">
-        <v>0.02406801798433245</v>
+        <v>0.02411378494098067</v>
       </c>
       <c r="AM21">
-        <v>0.06185923905598693</v>
+        <v>0.06197686856390942</v>
       </c>
       <c r="AN21">
-        <v>0.02859478397683858</v>
+        <v>0.02864915888379955</v>
       </c>
       <c r="AO21">
-        <v>0.04412697111910251</v>
+        <v>0.04421088152566525</v>
       </c>
       <c r="AP21">
-        <v>0.002531401058864179</v>
+        <v>0.002536214688411726</v>
       </c>
       <c r="AQ21">
         <v>38207126.39</v>
@@ -5158,7 +5158,7 @@
         <v>7428364.7</v>
       </c>
       <c r="AY21">
-        <v>246168918.087</v>
+        <v>231899577.655</v>
       </c>
       <c r="AZ21">
         <v>143809202.038</v>
@@ -5262,121 +5262,121 @@
         <v>44</v>
       </c>
       <c r="D22">
-        <v>0.01019711492080866</v>
+        <v>0.01018357423312893</v>
       </c>
       <c r="E22">
-        <v>0.02657817017385738</v>
+        <v>0.0265428771812592</v>
       </c>
       <c r="F22">
-        <v>0.04322693895215483</v>
+        <v>0.04316953815945537</v>
       </c>
       <c r="G22">
-        <v>0.005500490265608562</v>
+        <v>0.005493186197609877</v>
       </c>
       <c r="H22">
-        <v>0.2582426191066147</v>
+        <v>0.2578997002831951</v>
       </c>
       <c r="I22">
-        <v>0.003496031922601703</v>
+        <v>0.003491389562801902</v>
       </c>
       <c r="J22">
-        <v>0.00538539556114947</v>
+        <v>0.005378244326717805</v>
       </c>
       <c r="K22">
-        <v>0.001496626236443169</v>
+        <v>0.00149463887544956</v>
       </c>
       <c r="L22">
-        <v>0.02902470500220024</v>
+        <v>0.0303140572666792</v>
       </c>
       <c r="M22">
-        <v>0.002433639002244095</v>
+        <v>0.002430407387624615</v>
       </c>
       <c r="N22">
-        <v>0.01881444991077526</v>
+        <v>0.01878946631570095</v>
       </c>
       <c r="O22">
-        <v>0.04330674341991403</v>
+        <v>0.04324923665534099</v>
       </c>
       <c r="P22">
-        <v>0.01805385405129918</v>
+        <v>0.01802988044690004</v>
       </c>
       <c r="Q22">
-        <v>0.03485430277843216</v>
+        <v>0.03480801995903837</v>
       </c>
       <c r="R22">
-        <v>0.005541443375932548</v>
+        <v>0.005534084926544547</v>
       </c>
       <c r="S22">
-        <v>0.0194322752469677</v>
+        <v>0.01940647124533889</v>
       </c>
       <c r="T22">
-        <v>8.562205327723174E-05</v>
+        <v>8.550835626676084E-05</v>
       </c>
       <c r="U22">
-        <v>0.002557138927635852</v>
+        <v>0.002553743318206941</v>
       </c>
       <c r="V22">
-        <v>0.002864114966570729</v>
+        <v>0.002860311725502804</v>
       </c>
       <c r="W22">
-        <v>0.04977183116709501</v>
+        <v>0.04970573945131896</v>
       </c>
       <c r="X22">
-        <v>0.0002147906502012549</v>
+        <v>0.0002145054309864586</v>
       </c>
       <c r="Y22">
-        <v>0.01725966366181591</v>
+        <v>0.01723674465806663</v>
       </c>
       <c r="Z22">
-        <v>0.0009188683276284651</v>
+        <v>0.0009176481678931049</v>
       </c>
       <c r="AA22">
-        <v>0.001569105133426655</v>
+        <v>0.001567021528140906</v>
       </c>
       <c r="AB22">
-        <v>0.1192540923740278</v>
+        <v>0.1190957355807675</v>
       </c>
       <c r="AC22">
-        <v>0.01076830318704394</v>
+        <v>0.0107540040218949</v>
       </c>
       <c r="AD22">
-        <v>0.009287300647620705</v>
+        <v>0.009274968096851806</v>
       </c>
       <c r="AE22">
-        <v>0.005851301326675913</v>
+        <v>0.005843531418775512</v>
       </c>
       <c r="AF22">
-        <v>0.03497492842631811</v>
+        <v>0.03492848542885073</v>
       </c>
       <c r="AG22">
-        <v>0.01750299154131869</v>
+        <v>0.01747974942393916</v>
       </c>
       <c r="AH22">
-        <v>0.004357551527292728</v>
+        <v>0.004351765160782433</v>
       </c>
       <c r="AI22">
-        <v>0.0007083380599411227</v>
+        <v>0.000707397462084198</v>
       </c>
       <c r="AJ22">
-        <v>0.01594228043372634</v>
+        <v>0.01592111077525606</v>
       </c>
       <c r="AK22">
-        <v>0.0001631414267445596</v>
+        <v>0.0001629247922234888</v>
       </c>
       <c r="AL22">
-        <v>0.02152929639656054</v>
+        <v>0.02150070777313773</v>
       </c>
       <c r="AM22">
-        <v>0.0476151922481698</v>
+        <v>0.0475519643202657</v>
       </c>
       <c r="AN22">
-        <v>0.04153308717228263</v>
+        <v>0.04147793563519176</v>
       </c>
       <c r="AO22">
-        <v>0.03124054727813489</v>
+        <v>0.03119906314297292</v>
       </c>
       <c r="AP22">
-        <v>0.00176430798460759</v>
+        <v>0.001761965170627759</v>
       </c>
       <c r="AQ22">
         <v>96240973.38</v>
@@ -5403,7 +5403,7 @@
         <v>14125246.886</v>
       </c>
       <c r="AY22">
-        <v>273936881.478</v>
+        <v>286486287.786</v>
       </c>
       <c r="AZ22">
         <v>22968828.757</v>
@@ -5507,127 +5507,127 @@
         <v>44</v>
       </c>
       <c r="D23">
-        <v>0.008991555221980503</v>
+        <v>0.008992393629193768</v>
       </c>
       <c r="E23">
-        <v>0.0210090438314461</v>
+        <v>0.02112057751646715</v>
       </c>
       <c r="F23">
-        <v>0.04360585132891989</v>
+        <v>0.04360991730631669</v>
       </c>
       <c r="G23">
-        <v>0.006458414412537019</v>
+        <v>0.006459016619952316</v>
       </c>
       <c r="H23">
-        <v>0.279026935457433</v>
+        <v>0.2790529530027416</v>
       </c>
       <c r="I23">
-        <v>0.001944566260823947</v>
+        <v>0.001944747579665849</v>
       </c>
       <c r="J23">
-        <v>0.02164677351489241</v>
+        <v>0.02164879194336343</v>
       </c>
       <c r="K23">
-        <v>0.001372245495658285</v>
+        <v>0.001372373449109443</v>
       </c>
       <c r="L23">
-        <v>0.01971715641441017</v>
+        <v>0.01971899491795653</v>
       </c>
       <c r="M23">
-        <v>0.001568202529194386</v>
+        <v>0.001568348754433499</v>
       </c>
       <c r="N23">
-        <v>0.01734300801841185</v>
+        <v>0.01734462514722475</v>
       </c>
       <c r="O23">
-        <v>0.04239964583217499</v>
+        <v>0.04240359933832914</v>
       </c>
       <c r="P23">
-        <v>0.02177736738597258</v>
+        <v>0.02177939799151874</v>
       </c>
       <c r="Q23">
-        <v>0.02129373549316457</v>
+        <v>0.02129572100301176</v>
       </c>
       <c r="R23">
-        <v>0.004562644981081223</v>
+        <v>0.004563070419658785</v>
       </c>
       <c r="S23">
-        <v>0.01773764650041037</v>
+        <v>0.01773930042683412</v>
       </c>
       <c r="T23">
-        <v>0.000107558668160063</v>
+        <v>0.0001075686973442261</v>
       </c>
       <c r="U23">
-        <v>0.004608542917226225</v>
+        <v>0.004608972635503992</v>
       </c>
       <c r="V23">
-        <v>0.00305984748958623</v>
+        <v>0.003060132801542107</v>
       </c>
       <c r="W23">
-        <v>0.09009302658628056</v>
+        <v>0.09010142720680615</v>
       </c>
       <c r="X23">
-        <v>0.0001969814689834035</v>
+        <v>0.0001969998362936628</v>
       </c>
       <c r="Y23">
-        <v>0.00808047977961605</v>
+        <v>0.008081233234648757</v>
       </c>
       <c r="Z23">
-        <v>0.00860064849953422</v>
+        <v>0.008601450457100264</v>
       </c>
       <c r="AA23">
-        <v>0.005685584334192978</v>
+        <v>0.005686114479957501</v>
       </c>
       <c r="AB23">
-        <v>0.102621148254505</v>
+        <v>0.1026307170453099</v>
       </c>
       <c r="AC23">
-        <v>0.008072287961742369</v>
+        <v>0.008073040652938452</v>
       </c>
       <c r="AD23">
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>0.004309638759748681</v>
+        <v>0.00431004060705246</v>
       </c>
       <c r="AF23">
-        <v>0.02960626265027602</v>
+        <v>0.02960902325214644</v>
       </c>
       <c r="AG23">
-        <v>0.01314965141708789</v>
+        <v>0.01315087754119298</v>
       </c>
       <c r="AH23">
-        <v>0.003468498217282663</v>
+        <v>0.0034688216334051</v>
       </c>
       <c r="AI23">
-        <v>0.000637502415950014</v>
+        <v>0.0006375618591287312</v>
       </c>
       <c r="AJ23">
-        <v>0.008046316681950993</v>
+        <v>0.008047066951484997</v>
       </c>
       <c r="AK23">
         <v>0</v>
       </c>
       <c r="AL23">
-        <v>0.01559478007794899</v>
+        <v>0.01559623419526061</v>
       </c>
       <c r="AM23">
-        <v>0.04436842177789738</v>
+        <v>0.04437255886029763</v>
       </c>
       <c r="AN23">
-        <v>0.05736979369518854</v>
+        <v>0.05737514307554267</v>
       </c>
       <c r="AO23">
-        <v>0.0268840224512594</v>
+        <v>0.02662787726562988</v>
       </c>
       <c r="AP23">
-        <v>0.001790627499304024</v>
+        <v>0.001790794464303363</v>
       </c>
       <c r="AQ23">
         <v>132021674.08</v>
       </c>
       <c r="AR23">
-        <v>308472680.084</v>
+        <v>310081399.485</v>
       </c>
       <c r="AS23">
         <v>640258259</v>
@@ -5735,7 +5735,7 @@
         <v>842352186.944</v>
       </c>
       <c r="CB23">
-        <v>394734121.339</v>
+        <v>390936727.057</v>
       </c>
       <c r="CC23">
         <v>26291518.461</v>
@@ -5752,127 +5752,127 @@
         <v>44</v>
       </c>
       <c r="D24">
-        <v>0.002987447306672321</v>
+        <v>0.002987091409845908</v>
       </c>
       <c r="E24">
-        <v>0.01734795338349202</v>
+        <v>0.01747644050286585</v>
       </c>
       <c r="F24">
-        <v>0.03137160102888064</v>
+        <v>0.03136786370664544</v>
       </c>
       <c r="G24">
-        <v>0.003267286331239018</v>
+        <v>0.003266897096980835</v>
       </c>
       <c r="H24">
-        <v>0.3170469627068812</v>
+        <v>0.3170091926656826</v>
       </c>
       <c r="I24">
-        <v>0.001936153216246081</v>
+        <v>0.001935922560868972</v>
       </c>
       <c r="J24">
-        <v>0.005876340011885712</v>
+        <v>0.005875639959116082</v>
       </c>
       <c r="K24">
-        <v>0.02782198172647629</v>
+        <v>0.02781866727303677</v>
       </c>
       <c r="L24">
-        <v>0.02706386126804267</v>
+        <v>0.02706063713005895</v>
       </c>
       <c r="M24">
-        <v>0.004459891113391909</v>
+        <v>0.004459359803236291</v>
       </c>
       <c r="N24">
-        <v>0.02389308244861047</v>
+        <v>0.02389023604787305</v>
       </c>
       <c r="O24">
-        <v>0.04856443174055004</v>
+        <v>0.04855864622356554</v>
       </c>
       <c r="P24">
-        <v>0.012478387396582</v>
+        <v>0.01247689955959117</v>
       </c>
       <c r="Q24">
-        <v>0.03628275564080719</v>
+        <v>0.03626686895682619</v>
       </c>
       <c r="R24">
-        <v>0.003635994135854825</v>
+        <v>0.003635560977160805</v>
       </c>
       <c r="S24">
-        <v>0.00941921641642564</v>
+        <v>0.009418094298146792</v>
       </c>
       <c r="T24">
-        <v>0.0002854437823316491</v>
+        <v>0.0002854097772009061</v>
       </c>
       <c r="U24">
-        <v>0.001091417994705869</v>
+        <v>0.001091287973265912</v>
       </c>
       <c r="V24">
-        <v>0.003258722357063345</v>
+        <v>0.003258334143037795</v>
       </c>
       <c r="W24">
-        <v>0.03491855971688285</v>
+        <v>0.03491439984281296</v>
       </c>
       <c r="X24">
-        <v>0.0004127915481989018</v>
+        <v>0.0004127423720338038</v>
       </c>
       <c r="Y24">
-        <v>0.008023441386849222</v>
+        <v>0.008022485548290959</v>
       </c>
       <c r="Z24">
-        <v>0.003134894157259715</v>
+        <v>0.003134520694979989</v>
       </c>
       <c r="AA24">
-        <v>0.007495070676806504</v>
+        <v>0.007494177783445116</v>
       </c>
       <c r="AB24">
-        <v>0.1043176949391779</v>
+        <v>0.1043052674943541</v>
       </c>
       <c r="AC24">
-        <v>0.03634734926063504</v>
+        <v>0.03634301917380085</v>
       </c>
       <c r="AD24">
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>0.01488100629951912</v>
+        <v>0.01487923351413676</v>
       </c>
       <c r="AF24">
-        <v>0.02903838661485173</v>
+        <v>0.02903492725019036</v>
       </c>
       <c r="AG24">
-        <v>0.009449968626893247</v>
+        <v>0.009448842845080624</v>
       </c>
       <c r="AH24">
-        <v>0.002946783573279581</v>
+        <v>0.002946432520754063</v>
       </c>
       <c r="AI24">
-        <v>0.0008625302591186964</v>
+        <v>0.0008624275052454412</v>
       </c>
       <c r="AJ24">
-        <v>0.007876690341153056</v>
+        <v>0.007875751985156349</v>
       </c>
       <c r="AK24">
-        <v>3.837643433728309E-05</v>
+        <v>3.837186252402994E-05</v>
       </c>
       <c r="AL24">
-        <v>0.009886797372386086</v>
+        <v>0.009885619550839119</v>
       </c>
       <c r="AM24">
-        <v>0.04557403041598843</v>
+        <v>0.0455686011477447</v>
       </c>
       <c r="AN24">
-        <v>0.0407843334738804</v>
+        <v>0.04077947480580671</v>
       </c>
       <c r="AO24">
-        <v>0.0278998804335821</v>
+        <v>0.02789655670001148</v>
       </c>
       <c r="AP24">
-        <v>0.001949685800734927</v>
+        <v>0.001949453533210932</v>
       </c>
       <c r="AQ24">
         <v>39021412.06</v>
       </c>
       <c r="AR24">
-        <v>226595339.728</v>
+        <v>228300809.261</v>
       </c>
       <c r="AS24">
         <v>409769293</v>
@@ -5905,10 +5905,10 @@
         <v>634338452.824</v>
       </c>
       <c r="BC24">
-        <v>162990087.008</v>
+        <v>162990070.321</v>
       </c>
       <c r="BD24">
-        <v>473917767.644</v>
+        <v>473766699.28</v>
       </c>
       <c r="BE24">
         <v>47492595.135</v>
@@ -5997,118 +5997,118 @@
         <v>44</v>
       </c>
       <c r="D25">
-        <v>0.01210186615525645</v>
+        <v>0.01208704951663593</v>
       </c>
       <c r="E25">
-        <v>0.02735721579412556</v>
+        <v>0.02643982374949221</v>
       </c>
       <c r="F25">
-        <v>0.04093602118961438</v>
+        <v>0.04088590212328633</v>
       </c>
       <c r="G25">
-        <v>0.004984378667667422</v>
+        <v>0.005183068841766903</v>
       </c>
       <c r="H25">
-        <v>0.269529002869945</v>
+        <v>0.2691990112982287</v>
       </c>
       <c r="I25">
-        <v>0.001165618720197333</v>
+        <v>0.001164191622002318</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0.001198576794482298</v>
+        <v>0.001197109344834867</v>
       </c>
       <c r="L25">
-        <v>0.0428042720511083</v>
+        <v>0.04275186563524985</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>0.02428759353793548</v>
+        <v>0.0242578575871493</v>
       </c>
       <c r="O25">
-        <v>0.04772390689050637</v>
+        <v>0.04766547723404807</v>
       </c>
       <c r="P25">
-        <v>0.01368708230310077</v>
+        <v>0.01367032484300376</v>
       </c>
       <c r="Q25">
-        <v>0.04563919374870328</v>
+        <v>0.04708432879954196</v>
       </c>
       <c r="R25">
-        <v>0.004413185454821964</v>
+        <v>0.00440778227375794</v>
       </c>
       <c r="S25">
-        <v>0.01623609561976326</v>
+        <v>0.01621621733336346</v>
       </c>
       <c r="T25">
-        <v>0.001343376115377196</v>
+        <v>0.001341731384045877</v>
       </c>
       <c r="U25">
-        <v>0.005698802470479185</v>
+        <v>0.005691825274095457</v>
       </c>
       <c r="V25">
-        <v>0.004102334088102418</v>
+        <v>0.004097311490686097</v>
       </c>
       <c r="W25">
-        <v>0.02032223003142697</v>
+        <v>0.02029734898130827</v>
       </c>
       <c r="X25">
-        <v>0.001883062209028499</v>
+        <v>0.001880756725568908</v>
       </c>
       <c r="Y25">
-        <v>0.03153083011841133</v>
+        <v>0.0311636032437043</v>
       </c>
       <c r="Z25">
-        <v>0.0003845031294804331</v>
+        <v>0.0003840323720084133</v>
       </c>
       <c r="AA25">
-        <v>0.008690993128560006</v>
+        <v>0.008680352513072505</v>
       </c>
       <c r="AB25">
-        <v>0.08949504759549395</v>
+        <v>0.08940042671814177</v>
       </c>
       <c r="AC25">
-        <v>0.05896702751375309</v>
+        <v>0.05889483260381203</v>
       </c>
       <c r="AD25">
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0.01256737278904621</v>
+        <v>0.01255198621819542</v>
       </c>
       <c r="AF25">
-        <v>0.03070674109653534</v>
+        <v>0.03066914601159519</v>
       </c>
       <c r="AG25">
-        <v>0.0126941246021518</v>
+        <v>0.01267858284566391</v>
       </c>
       <c r="AH25">
-        <v>0.002790756473867903</v>
+        <v>0.002787339676026917</v>
       </c>
       <c r="AI25">
-        <v>0.001131703902822398</v>
+        <v>0.001116760076421529</v>
       </c>
       <c r="AJ25">
-        <v>0.0115919572208561</v>
+        <v>0.01157776487739084</v>
       </c>
       <c r="AK25">
-        <v>0.0001640984223179837</v>
+        <v>0.0001638975122277141</v>
       </c>
       <c r="AL25">
-        <v>0.009771287951403706</v>
+        <v>0.009759324702052274</v>
       </c>
       <c r="AM25">
-        <v>0.05670626146566589</v>
+        <v>0.0566368344721032</v>
       </c>
       <c r="AN25">
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.04520157148030197</v>
+        <v>0.04514622998659255</v>
       </c>
       <c r="AP25">
         <v>0</v>
@@ -6117,13 +6117,13 @@
         <v>145623126.58</v>
       </c>
       <c r="AR25">
-        <v>329192477.206</v>
+        <v>318543395.998</v>
       </c>
       <c r="AS25">
         <v>492587781</v>
       </c>
       <c r="AT25">
-        <v>59977593.235</v>
+        <v>62444907.583</v>
       </c>
       <c r="AU25">
         <v>3243273029</v>
@@ -6150,10 +6150,10 @@
         <v>574267178.702</v>
       </c>
       <c r="BC25">
-        <v>164698212.091</v>
+        <v>164698212.104</v>
       </c>
       <c r="BD25">
-        <v>549181589.27</v>
+        <v>567265581.503</v>
       </c>
       <c r="BE25">
         <v>53104360.589</v>
@@ -6177,7 +6177,7 @@
         <v>22659100.911</v>
       </c>
       <c r="BL25">
-        <v>379414051.238</v>
+        <v>375454848.067</v>
       </c>
       <c r="BM25">
         <v>4626769.721</v>
@@ -6186,7 +6186,7 @@
         <v>104579705</v>
       </c>
       <c r="BO25">
-        <v>1076904047.449</v>
+        <v>1077084166.683</v>
       </c>
       <c r="BP25">
         <v>709556923</v>
@@ -6207,7 +6207,7 @@
         <v>33581488.841</v>
       </c>
       <c r="BV25">
-        <v>13617921.284</v>
+        <v>13454573.322</v>
       </c>
       <c r="BW25">
         <v>139487334.6</v>
